--- a/research/existing-systems/Existing_Systems.xlsx
+++ b/research/existing-systems/Existing_Systems.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\FraudLens\research\existing-systems\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28480027-CB94-4061-B79A-8F202C471EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,41 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>System ID</t>
+  </si>
+  <si>
+    <t>System / Technology</t>
+  </si>
+  <si>
+    <t>Organization</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Key Capabilities</t>
+  </si>
+  <si>
+    <t>Technology / AI</t>
+  </si>
+  <si>
+    <t>Limitations / Undisclosed Info</t>
+  </si>
+  <si>
+    <t>FraudLens Relevance</t>
+  </si>
+  <si>
+    <t>Source / Link</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +66,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +97,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +401,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="18.77734375" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>